--- a/resources/templates/plugin_output.xlsx
+++ b/resources/templates/plugin_output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fl\Documents\Python\QGIS-Plugin_FW_Massenermittlung\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fl\Documents\Python\QGIS-Plugin_DHN\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC483944-D783-4A3A-8428-41A83605377E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238FBD68-2AB8-4FCD-A685-F981EAFBA427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1488" yWindow="780" windowWidth="28236" windowHeight="15348" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1104" yWindow="900" windowWidth="28236" windowHeight="15348" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formteile" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>fid</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Bogen-Winkel</t>
   </si>
   <si>
+    <t>Leistung</t>
+  </si>
+  <si>
     <t>Verbundene Leitungen</t>
   </si>
   <si>
@@ -58,43 +61,55 @@
     <t>Schnittpunkt ohne Verbindung - die Linien müssen mit Endpunkten verbunden werden.</t>
   </si>
   <si>
+    <t>Hausanschluss</t>
+  </si>
+  <si>
+    <t>613</t>
+  </si>
+  <si>
+    <t>Bogen</t>
+  </si>
+  <si>
+    <t>Bogen in Anschlussleitung (Anschluss nicht im 90° Winkel)</t>
+  </si>
+  <si>
     <t>T-Stück</t>
   </si>
   <si>
-    <t>857 / 862 / 864</t>
-  </si>
-  <si>
-    <t>Hauptleitung: 862 (DN50) &amp; 864 (DN50)</t>
-  </si>
-  <si>
-    <t>Bogen</t>
-  </si>
-  <si>
-    <t>862 / 875</t>
-  </si>
-  <si>
-    <t>Hausanschluss</t>
-  </si>
-  <si>
-    <t>848</t>
+    <t>597 / 608 / 613</t>
+  </si>
+  <si>
+    <t>Hauptleitung: 608 (DN80) &amp; 597 (DN80)</t>
   </si>
   <si>
     <t>Reduzierung</t>
   </si>
   <si>
-    <t>849</t>
-  </si>
-  <si>
-    <t>Reduzierung von DN65 auf DN50</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Dimension</t>
+    <t>633</t>
+  </si>
+  <si>
+    <t>Reduzierung von DN40 auf DN32</t>
+  </si>
+  <si>
+    <t>Original ID</t>
+  </si>
+  <si>
+    <t>Original Leistung</t>
   </si>
   <si>
     <t>Trassenlänge</t>
+  </si>
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Anschlussleitung</t>
+  </si>
+  <si>
+    <t>Hauptleitung</t>
+  </si>
+  <si>
+    <t>Original Dimension</t>
   </si>
 </sst>
 </file>
@@ -464,7 +479,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1024" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+      <c r="F3">
+        <v>90.313059999999993</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="E4">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>80</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1024" width="15"/>
@@ -475,148 +626,62 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
+      <c r="B2">
+        <v>613</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>90.313059999999993</v>
+      </c>
+      <c r="E2">
+        <v>15.08003494579712</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
+      <c r="B3">
+        <v>612</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>63.31353</v>
+      </c>
+      <c r="E3">
+        <v>4.2919095285150126</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>50</v>
-      </c>
-      <c r="E4">
-        <v>82</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>65</v>
-      </c>
-      <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1024" width="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>920</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>0.30661180373975172</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
